--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,45 +1321,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124902370</v>
+        <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Trehörningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443757</v>
+        <v>443764</v>
       </c>
       <c r="R8" t="n">
-        <v>6675528</v>
+        <v>6675476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,17 +1395,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fjolårsfruktkropp</t>
+          <t>Noterad efter utförd naturvårdsbränning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,44 +1420,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124902396</v>
+        <v>124902370</v>
       </c>
       <c r="B9" t="n">
-        <v>91930</v>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443498</v>
+        <v>443757</v>
       </c>
       <c r="R9" t="n">
-        <v>6675516</v>
+        <v>6675528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,6 +1505,11 @@
           <t>2025-05-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1504,21 +1518,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1535,32 +1534,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879884</v>
+        <v>124902396</v>
       </c>
       <c r="B10" t="n">
-        <v>91282</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443902</v>
+        <v>443498</v>
       </c>
       <c r="R10" t="n">
-        <v>6675241</v>
+        <v>6675516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,12 +1599,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,32 +1646,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902368</v>
+        <v>124879884</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443468</v>
+        <v>443902</v>
       </c>
       <c r="R11" t="n">
-        <v>6675294</v>
+        <v>6675241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,12 +1711,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124902373</v>
+        <v>124902368</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1794,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443657</v>
+        <v>443468</v>
       </c>
       <c r="R12" t="n">
-        <v>6675694</v>
+        <v>6675294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,17 +1842,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1871,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124902376</v>
+        <v>124902373</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1906,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443630</v>
+        <v>443657</v>
       </c>
       <c r="R13" t="n">
-        <v>6675717</v>
+        <v>6675694</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,17 +1954,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1983,7 +1982,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124902382</v>
+        <v>124902376</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2018,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443583</v>
+        <v>443630</v>
       </c>
       <c r="R14" t="n">
-        <v>6675786</v>
+        <v>6675717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2094,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124902384</v>
+        <v>124902382</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2130,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443557</v>
+        <v>443583</v>
       </c>
       <c r="R15" t="n">
-        <v>6675793</v>
+        <v>6675786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,7 +2206,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124902389</v>
+        <v>124902384</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2242,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443488</v>
+        <v>443557</v>
       </c>
       <c r="R16" t="n">
-        <v>6675673</v>
+        <v>6675793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,7 +2318,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902395</v>
+        <v>124902389</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2354,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443490</v>
+        <v>443488</v>
       </c>
       <c r="R17" t="n">
-        <v>6675536</v>
+        <v>6675673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,32 +2430,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124879896</v>
+        <v>124902395</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2466,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444190</v>
+        <v>443490</v>
       </c>
       <c r="R18" t="n">
-        <v>6674932</v>
+        <v>6675536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,12 +2495,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,45 +2542,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124902386</v>
+        <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Nothusberget , Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443508</v>
+        <v>443503</v>
       </c>
       <c r="R19" t="n">
-        <v>6675697</v>
+        <v>6675793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,12 +2607,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Noterad efter utförd naturvårdsbränning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,22 +2647,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124879887</v>
+        <v>124879896</v>
       </c>
       <c r="B20" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,21 +2670,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444079</v>
+        <v>444190</v>
       </c>
       <c r="R20" t="n">
-        <v>6675299</v>
+        <v>6674932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,10 +2771,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124879889</v>
+        <v>124902386</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,21 +2782,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2802,10 +2806,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444104</v>
+        <v>443508</v>
       </c>
       <c r="R21" t="n">
-        <v>6675222</v>
+        <v>6675697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,12 +2836,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,10 +2883,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124879892</v>
+        <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,34 +2894,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Trehörningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444190</v>
+        <v>443849</v>
       </c>
       <c r="R22" t="n">
-        <v>6674933</v>
+        <v>6675226</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,12 +2948,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2979,19 +2983,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124902369</v>
+        <v>124879887</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -3026,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443958</v>
+        <v>444079</v>
       </c>
       <c r="R23" t="n">
-        <v>6675653</v>
+        <v>6675299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,12 +3060,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,7 +3107,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124902380</v>
+        <v>124879889</v>
       </c>
       <c r="B24" t="n">
         <v>79946</v>
@@ -3138,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443596</v>
+        <v>444104</v>
       </c>
       <c r="R24" t="n">
-        <v>6675775</v>
+        <v>6675222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,12 +3172,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3215,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124902391</v>
+        <v>124879892</v>
       </c>
       <c r="B25" t="n">
         <v>79946</v>
@@ -3250,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443488</v>
+        <v>444190</v>
       </c>
       <c r="R25" t="n">
-        <v>6675661</v>
+        <v>6674933</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,12 +3284,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,7 +3331,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124902393</v>
+        <v>124902369</v>
       </c>
       <c r="B26" t="n">
         <v>79946</v>
@@ -3362,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443491</v>
+        <v>443958</v>
       </c>
       <c r="R26" t="n">
-        <v>6675646</v>
+        <v>6675653</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3439,7 +3443,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124902398</v>
+        <v>124902380</v>
       </c>
       <c r="B27" t="n">
         <v>79946</v>
@@ -3474,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443533</v>
+        <v>443596</v>
       </c>
       <c r="R27" t="n">
-        <v>6675433</v>
+        <v>6675775</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3551,7 +3555,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124902399</v>
+        <v>124902391</v>
       </c>
       <c r="B28" t="n">
         <v>79946</v>
@@ -3586,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443596</v>
+        <v>443488</v>
       </c>
       <c r="R28" t="n">
-        <v>6675349</v>
+        <v>6675661</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3663,50 +3667,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124902397</v>
+        <v>124902393</v>
       </c>
       <c r="B29" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443519</v>
+        <v>443491</v>
       </c>
       <c r="R29" t="n">
-        <v>6675478</v>
+        <v>6675646</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3780,50 +3779,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124902400</v>
+        <v>124902398</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443619</v>
+        <v>443533</v>
       </c>
       <c r="R30" t="n">
-        <v>6675118</v>
+        <v>6675433</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,10 +3891,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124879894</v>
+        <v>124902399</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,21 +3902,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3926,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444190</v>
+        <v>443596</v>
       </c>
       <c r="R31" t="n">
-        <v>6674932</v>
+        <v>6675349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,12 +3956,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4009,45 +4003,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902372</v>
+        <v>124902397</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443679</v>
+        <v>443519</v>
       </c>
       <c r="R32" t="n">
-        <v>6675698</v>
+        <v>6675478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,45 +4120,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124902378</v>
+        <v>124902400</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443631</v>
+        <v>443619</v>
       </c>
       <c r="R33" t="n">
-        <v>6675735</v>
+        <v>6675118</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4233,7 +4237,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124902388</v>
+        <v>124879894</v>
       </c>
       <c r="B34" t="n">
         <v>79085</v>
@@ -4268,10 +4272,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443508</v>
+        <v>444190</v>
       </c>
       <c r="R34" t="n">
-        <v>6675696</v>
+        <v>6674932</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,12 +4302,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,7 +4349,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124902392</v>
+        <v>124902372</v>
       </c>
       <c r="B35" t="n">
         <v>79085</v>
@@ -4380,10 +4384,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443487</v>
+        <v>443679</v>
       </c>
       <c r="R35" t="n">
-        <v>6675661</v>
+        <v>6675698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,32 +4461,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124902374</v>
+        <v>124902378</v>
       </c>
       <c r="B36" t="n">
-        <v>79515</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230552</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4492,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443649</v>
+        <v>443631</v>
       </c>
       <c r="R36" t="n">
-        <v>6675709</v>
+        <v>6675735</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,17 +4545,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4566,6 +4570,342 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124902388</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>443508</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6675696</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124902392</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>443487</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6675661</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124902374</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>443649</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6675709</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879885</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879886</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902385</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902394</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126833427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135483343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902370</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902396</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879884</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902368</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902373</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902376</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902382</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902384</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2427,6 +2507,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902389</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902395</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2656,6 +2746,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135482860</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879896</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2880,6 +2980,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902386</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2992,6 +3097,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135483533</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3104,6 +3214,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879887</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879889</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879892</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3440,6 +3565,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902369</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3552,6 +3682,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902380</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3664,6 +3799,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902391</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3776,6 +3916,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902393</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3888,6 +4033,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902398</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4000,6 +4150,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902399</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4117,6 +4272,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902397</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4234,6 +4394,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902400</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4346,6 +4511,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879894</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4458,6 +4628,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902372</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4570,6 +4745,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902378</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4682,6 +4862,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902388</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4794,6 +4979,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902392</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4906,8 +5096,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,45 +1356,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124902370</v>
+        <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93201</v>
+        <v>93345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Trehörningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443757</v>
+        <v>443764</v>
       </c>
       <c r="R8" t="n">
-        <v>6675528</v>
+        <v>6675476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,17 +1430,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fjolårsfruktkropp</t>
+          <t>Noterad efter utförd naturvårdsbränning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,49 +1455,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902370</t>
+          <t>https://artportalen.se/Sighting/135483343</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124902396</v>
+        <v>124902370</v>
       </c>
       <c r="B9" t="n">
-        <v>91930</v>
+        <v>93201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443498</v>
+        <v>443757</v>
       </c>
       <c r="R9" t="n">
-        <v>6675516</v>
+        <v>6675528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,6 +1545,11 @@
           <t>2025-05-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1544,21 +1558,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1574,38 +1573,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902396</t>
+          <t>https://artportalen.se/Sighting/124902370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879884</v>
+        <v>124902396</v>
       </c>
       <c r="B10" t="n">
-        <v>91282</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443902</v>
+        <v>443498</v>
       </c>
       <c r="R10" t="n">
-        <v>6675241</v>
+        <v>6675516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1644,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,38 +1690,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879884</t>
+          <t>https://artportalen.se/Sighting/124902396</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902368</v>
+        <v>124879884</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443468</v>
+        <v>443902</v>
       </c>
       <c r="R11" t="n">
-        <v>6675294</v>
+        <v>6675241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,12 +1761,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,13 +1807,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902368</t>
+          <t>https://artportalen.se/Sighting/124879884</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124902373</v>
+        <v>124902368</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1849,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443657</v>
+        <v>443468</v>
       </c>
       <c r="R12" t="n">
-        <v>6675694</v>
+        <v>6675294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,17 +1897,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,13 +1924,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902373</t>
+          <t>https://artportalen.se/Sighting/124902368</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124902376</v>
+        <v>124902373</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1966,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443630</v>
+        <v>443657</v>
       </c>
       <c r="R13" t="n">
-        <v>6675717</v>
+        <v>6675694</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,17 +2014,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2042,13 +2041,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902376</t>
+          <t>https://artportalen.se/Sighting/124902373</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124902382</v>
+        <v>124902376</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2083,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443583</v>
+        <v>443630</v>
       </c>
       <c r="R14" t="n">
-        <v>6675786</v>
+        <v>6675717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,13 +2158,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902382</t>
+          <t>https://artportalen.se/Sighting/124902376</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124902384</v>
+        <v>124902382</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2200,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443557</v>
+        <v>443583</v>
       </c>
       <c r="R15" t="n">
-        <v>6675793</v>
+        <v>6675786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,13 +2275,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902384</t>
+          <t>https://artportalen.se/Sighting/124902382</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124902389</v>
+        <v>124902384</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2317,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443488</v>
+        <v>443557</v>
       </c>
       <c r="R16" t="n">
-        <v>6675673</v>
+        <v>6675793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2393,13 +2392,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902389</t>
+          <t>https://artportalen.se/Sighting/124902384</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902395</v>
+        <v>124902389</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2434,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443490</v>
+        <v>443488</v>
       </c>
       <c r="R17" t="n">
-        <v>6675536</v>
+        <v>6675673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,38 +2509,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902395</t>
+          <t>https://artportalen.se/Sighting/124902389</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124879896</v>
+        <v>124902395</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2550,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444190</v>
+        <v>443490</v>
       </c>
       <c r="R18" t="n">
-        <v>6674932</v>
+        <v>6675536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,12 +2580,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,51 +2626,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879896</t>
+          <t>https://artportalen.se/Sighting/124902395</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124902386</v>
+        <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Nothusberget , Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443508</v>
+        <v>443503</v>
       </c>
       <c r="R19" t="n">
-        <v>6675697</v>
+        <v>6675793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,12 +2697,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Noterad efter utförd naturvårdsbränning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,27 +2737,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902386</t>
+          <t>https://artportalen.se/Sighting/135482860</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124879887</v>
+        <v>124879896</v>
       </c>
       <c r="B20" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,21 +2765,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2785,10 +2789,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444079</v>
+        <v>444190</v>
       </c>
       <c r="R20" t="n">
-        <v>6675299</v>
+        <v>6674932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,16 +2865,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879887</t>
+          <t>https://artportalen.se/Sighting/124879896</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124879889</v>
+        <v>124902386</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,21 +2882,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444104</v>
+        <v>443508</v>
       </c>
       <c r="R21" t="n">
-        <v>6675222</v>
+        <v>6675697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,12 +2936,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,16 +2982,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879889</t>
+          <t>https://artportalen.se/Sighting/124902386</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124879892</v>
+        <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>79198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,34 +2999,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nothusberget, Tyngsjö, Dlr</t>
+          <t>Trehörningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444190</v>
+        <v>443849</v>
       </c>
       <c r="R22" t="n">
-        <v>6674933</v>
+        <v>6675226</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,12 +3053,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,24 +3088,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879892</t>
+          <t>https://artportalen.se/Sighting/135483533</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124902369</v>
+        <v>124879887</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -3136,10 +3140,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443958</v>
+        <v>444079</v>
       </c>
       <c r="R23" t="n">
-        <v>6675653</v>
+        <v>6675299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,12 +3170,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,13 +3216,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902369</t>
+          <t>https://artportalen.se/Sighting/124879887</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124902380</v>
+        <v>124879889</v>
       </c>
       <c r="B24" t="n">
         <v>79946</v>
@@ -3253,10 +3257,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443596</v>
+        <v>444104</v>
       </c>
       <c r="R24" t="n">
-        <v>6675775</v>
+        <v>6675222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,12 +3287,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,13 +3333,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902380</t>
+          <t>https://artportalen.se/Sighting/124879889</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124902391</v>
+        <v>124879892</v>
       </c>
       <c r="B25" t="n">
         <v>79946</v>
@@ -3370,10 +3374,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443488</v>
+        <v>444190</v>
       </c>
       <c r="R25" t="n">
-        <v>6675661</v>
+        <v>6674933</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,12 +3404,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,13 +3450,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902391</t>
+          <t>https://artportalen.se/Sighting/124879892</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124902393</v>
+        <v>124902369</v>
       </c>
       <c r="B26" t="n">
         <v>79946</v>
@@ -3487,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443491</v>
+        <v>443958</v>
       </c>
       <c r="R26" t="n">
-        <v>6675646</v>
+        <v>6675653</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3563,13 +3567,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902393</t>
+          <t>https://artportalen.se/Sighting/124902369</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124902398</v>
+        <v>124902380</v>
       </c>
       <c r="B27" t="n">
         <v>79946</v>
@@ -3604,10 +3608,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443533</v>
+        <v>443596</v>
       </c>
       <c r="R27" t="n">
-        <v>6675433</v>
+        <v>6675775</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3680,13 +3684,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902398</t>
+          <t>https://artportalen.se/Sighting/124902380</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124902399</v>
+        <v>124902391</v>
       </c>
       <c r="B28" t="n">
         <v>79946</v>
@@ -3721,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443596</v>
+        <v>443488</v>
       </c>
       <c r="R28" t="n">
-        <v>6675349</v>
+        <v>6675661</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3797,56 +3801,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902399</t>
+          <t>https://artportalen.se/Sighting/124902391</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124902397</v>
+        <v>124902393</v>
       </c>
       <c r="B29" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443519</v>
+        <v>443491</v>
       </c>
       <c r="R29" t="n">
-        <v>6675478</v>
+        <v>6675646</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3919,56 +3918,51 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902397</t>
+          <t>https://artportalen.se/Sighting/124902393</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124902400</v>
+        <v>124902398</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443619</v>
+        <v>443533</v>
       </c>
       <c r="R30" t="n">
-        <v>6675118</v>
+        <v>6675433</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4041,16 +4035,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902400</t>
+          <t>https://artportalen.se/Sighting/124902398</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124879894</v>
+        <v>124902399</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4058,21 +4052,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4082,10 +4076,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444190</v>
+        <v>443596</v>
       </c>
       <c r="R31" t="n">
-        <v>6674932</v>
+        <v>6675349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4112,12 +4106,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4158,51 +4152,56 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124879894</t>
+          <t>https://artportalen.se/Sighting/124902399</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902372</v>
+        <v>124902397</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443679</v>
+        <v>443519</v>
       </c>
       <c r="R32" t="n">
-        <v>6675698</v>
+        <v>6675478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4275,51 +4274,56 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902372</t>
+          <t>https://artportalen.se/Sighting/124902397</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124902378</v>
+        <v>124902400</v>
       </c>
       <c r="B33" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nothusberget, Tyngsjö, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443631</v>
+        <v>443619</v>
       </c>
       <c r="R33" t="n">
-        <v>6675735</v>
+        <v>6675118</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4392,13 +4396,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902378</t>
+          <t>https://artportalen.se/Sighting/124902400</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124902388</v>
+        <v>124879894</v>
       </c>
       <c r="B34" t="n">
         <v>79085</v>
@@ -4433,10 +4437,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443508</v>
+        <v>444190</v>
       </c>
       <c r="R34" t="n">
-        <v>6675696</v>
+        <v>6674932</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4463,12 +4467,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,13 +4513,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902388</t>
+          <t>https://artportalen.se/Sighting/124879894</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124902392</v>
+        <v>124902372</v>
       </c>
       <c r="B35" t="n">
         <v>79085</v>
@@ -4550,10 +4554,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443487</v>
+        <v>443679</v>
       </c>
       <c r="R35" t="n">
-        <v>6675661</v>
+        <v>6675698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4626,38 +4630,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124902392</t>
+          <t>https://artportalen.se/Sighting/124902372</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124902374</v>
+        <v>124902378</v>
       </c>
       <c r="B36" t="n">
-        <v>79515</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230552</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4667,10 +4671,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443649</v>
+        <v>443631</v>
       </c>
       <c r="R36" t="n">
-        <v>6675709</v>
+        <v>6675735</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4716,17 +4720,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4742,6 +4746,357 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902378</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124902388</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>443508</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6675696</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902388</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124902392</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>443487</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6675661</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902392</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124902374</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nothusberget, Tyngsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>443649</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6675709</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124902374</t>
         </is>
@@ -4784,6 +5139,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/S 402-2026 artfynd.xlsx
+++ b/artfynd/S 402-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>135483343</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135482860</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135483533</v>
       </c>
       <c r="B22" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
